--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EL VENTERO CBV.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EL VENTERO CBV.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>96.1831</v>
+        <v>88.9402</v>
       </c>
       <c r="E2" t="n">
-        <v>49.2318</v>
+        <v>45.24</v>
       </c>
       <c r="F2" t="n">
-        <v>46.9517</v>
+        <v>43.6998</v>
       </c>
       <c r="G2" t="n">
         <v>76.1018</v>
@@ -610,13 +610,13 @@
         <v>61.0127</v>
       </c>
       <c r="S2" t="n">
-        <v>24.2151</v>
+        <v>16.9717</v>
       </c>
       <c r="T2" t="n">
-        <v>9.117599999999999</v>
+        <v>5.1258</v>
       </c>
       <c r="U2" t="n">
-        <v>15.0972</v>
+        <v>11.8459</v>
       </c>
       <c r="V2" t="n">
         <v>-4.3266</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>85.75839999999999</v>
+        <v>73.93380000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>50.4431</v>
+        <v>31.3602</v>
       </c>
       <c r="F3" t="n">
-        <v>35.3153</v>
+        <v>42.5736</v>
       </c>
       <c r="G3" t="n">
-        <v>35.0887</v>
+        <v>25.9286</v>
       </c>
       <c r="H3" t="n">
-        <v>26.9742</v>
+        <v>29.8579</v>
       </c>
       <c r="I3" t="n">
-        <v>8.1142</v>
+        <v>-3.9294</v>
       </c>
       <c r="J3" t="n">
-        <v>47.473</v>
+        <v>41.6133</v>
       </c>
       <c r="K3" t="n">
-        <v>36.6489</v>
+        <v>42.2241</v>
       </c>
       <c r="L3" t="n">
-        <v>10.8245</v>
+        <v>-0.6108999999999996</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.3846</v>
+        <v>-15.6844</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.6744</v>
+        <v>-12.3663</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.7102</v>
+        <v>-3.3182</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9650000000000001</v>
+        <v>13.3223</v>
       </c>
       <c r="Q3" t="n">
-        <v>-49.6215</v>
+        <v>-48.2699</v>
       </c>
       <c r="R3" t="n">
-        <v>48.6553</v>
+        <v>61.5916</v>
       </c>
       <c r="S3" t="n">
-        <v>57.0658</v>
+        <v>3.5167</v>
       </c>
       <c r="T3" t="n">
-        <v>34.2437</v>
+        <v>-0.3145999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>22.822</v>
+        <v>3.8313</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.431000000000001</v>
+        <v>31.1662</v>
       </c>
       <c r="W3" t="n">
-        <v>18.3472</v>
+        <v>38.3312</v>
       </c>
       <c r="X3" t="n">
-        <v>-23.7779</v>
+        <v>-7.165</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>56.0548</v>
+        <v>66.0292</v>
       </c>
       <c r="E4" t="n">
-        <v>27.2555</v>
+        <v>33.9089</v>
       </c>
       <c r="F4" t="n">
-        <v>28.7993</v>
+        <v>32.1197</v>
       </c>
       <c r="G4" t="n">
         <v>25.8579</v>
@@ -766,13 +766,13 @@
         <v>61.3986</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01789999999999997</v>
+        <v>9.992099999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.720400000000001</v>
+        <v>0.9331999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>5.7386</v>
+        <v>9.059200000000001</v>
       </c>
       <c r="V4" t="n">
         <v>3.5339</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>48.1738</v>
+        <v>55.3744</v>
       </c>
       <c r="E5" t="n">
-        <v>16.3293</v>
+        <v>28.814</v>
       </c>
       <c r="F5" t="n">
-        <v>31.845</v>
+        <v>26.5596</v>
       </c>
       <c r="G5" t="n">
-        <v>25.9286</v>
+        <v>35.0887</v>
       </c>
       <c r="H5" t="n">
-        <v>29.8579</v>
+        <v>26.9742</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.9294</v>
+        <v>8.1142</v>
       </c>
       <c r="J5" t="n">
-        <v>41.6133</v>
+        <v>47.473</v>
       </c>
       <c r="K5" t="n">
-        <v>42.2241</v>
+        <v>36.6489</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6108999999999996</v>
+        <v>10.8245</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.6844</v>
+        <v>-12.3846</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.3663</v>
+        <v>-9.6744</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3182</v>
+        <v>-2.7102</v>
       </c>
       <c r="P5" t="n">
-        <v>13.3223</v>
+        <v>-0.9650000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.2699</v>
+        <v>-49.6215</v>
       </c>
       <c r="R5" t="n">
-        <v>61.5916</v>
+        <v>48.6553</v>
       </c>
       <c r="S5" t="n">
-        <v>-22.2428</v>
+        <v>26.6814</v>
       </c>
       <c r="T5" t="n">
-        <v>-15.3456</v>
+        <v>12.6151</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.8977</v>
+        <v>14.0663</v>
       </c>
       <c r="V5" t="n">
-        <v>31.1662</v>
+        <v>-5.431000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>38.3312</v>
+        <v>18.3472</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.165</v>
+        <v>-23.7779</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>25.3411</v>
+        <v>40.0585</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4824</v>
+        <v>20.3836</v>
       </c>
       <c r="F6" t="n">
-        <v>14.8587</v>
+        <v>19.6751</v>
       </c>
       <c r="G6" t="n">
         <v>40.0606</v>
@@ -922,13 +922,13 @@
         <v>50.2003</v>
       </c>
       <c r="S6" t="n">
-        <v>-9.9451</v>
+        <v>4.7722</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.661299999999999</v>
+        <v>0.2399000000000002</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2838000000000003</v>
+        <v>4.5322</v>
       </c>
       <c r="V6" t="n">
         <v>9.513999999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>12.7299</v>
+        <v>9.210100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>27.2972</v>
+        <v>6.395100000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.5672</v>
+        <v>2.8149</v>
       </c>
       <c r="G7" t="n">
-        <v>3.777499999999999</v>
+        <v>13.6318</v>
       </c>
       <c r="H7" t="n">
-        <v>7.7478</v>
+        <v>2.0979</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.9701</v>
+        <v>11.5339</v>
       </c>
       <c r="J7" t="n">
-        <v>14.0001</v>
+        <v>15.9454</v>
       </c>
       <c r="K7" t="n">
-        <v>13.5492</v>
+        <v>5.4148</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4503999999999994</v>
+        <v>10.5305</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.2223</v>
+        <v>-2.3134</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.8016</v>
+        <v>-3.3169</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.420199999999999</v>
+        <v>1.0035</v>
       </c>
       <c r="P7" t="n">
-        <v>13.1291</v>
+        <v>4.440799999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.4119</v>
+        <v>-11.971</v>
       </c>
       <c r="R7" t="n">
-        <v>29.5408</v>
+        <v>16.4117</v>
       </c>
       <c r="S7" t="n">
-        <v>12.4264</v>
+        <v>-0.5449000000000002</v>
       </c>
       <c r="T7" t="n">
-        <v>13.591</v>
+        <v>0.2934000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1648</v>
+        <v>-0.8382000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-16.6037</v>
+        <v>-8.3177</v>
       </c>
       <c r="W7" t="n">
-        <v>16.1177</v>
+        <v>2.1271</v>
       </c>
       <c r="X7" t="n">
-        <v>-32.7213</v>
+        <v>-10.4448</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>6.184899999999999</v>
+        <v>5.543</v>
       </c>
       <c r="E8" t="n">
-        <v>6.9533</v>
+        <v>17.9615</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7683999999999997</v>
+        <v>-12.4185</v>
       </c>
       <c r="G8" t="n">
-        <v>13.6318</v>
+        <v>3.777499999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0979</v>
+        <v>7.7478</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5339</v>
+        <v>-3.9701</v>
       </c>
       <c r="J8" t="n">
-        <v>15.9454</v>
+        <v>14.0001</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4148</v>
+        <v>13.5492</v>
       </c>
       <c r="L8" t="n">
-        <v>10.5305</v>
+        <v>0.4503999999999994</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3134</v>
+        <v>-10.2223</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.3169</v>
+        <v>-5.8016</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0035</v>
+        <v>-4.420199999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>4.440799999999999</v>
+        <v>13.1291</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.971</v>
+        <v>-16.4119</v>
       </c>
       <c r="R8" t="n">
-        <v>16.4117</v>
+        <v>29.5408</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.57</v>
+        <v>5.2398</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8518000000000001</v>
+        <v>4.2557</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.422000000000001</v>
+        <v>0.9840999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.3177</v>
+        <v>-16.6037</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1271</v>
+        <v>16.1177</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.4448</v>
+        <v>-32.7213</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5.6761</v>
+        <v>4.9412</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6318</v>
+        <v>3.6596</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0442</v>
+        <v>1.2813</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3148000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>4.633900000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>3.431</v>
+        <v>2.696</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5366</v>
+        <v>1.5643</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8944000000000001</v>
+        <v>1.1315</v>
       </c>
       <c r="V9" t="n">
         <v>0.243</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MAÏGA</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3509</v>
+        <v>1.2067</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1145</v>
+        <v>3.4332</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2365</v>
+        <v>-2.2262</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9080999999999999</v>
+        <v>-1.9542</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0686</v>
+        <v>-2.1486</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1605</v>
+        <v>0.1943999999999995</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6524</v>
+        <v>10.2057</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3442</v>
+        <v>6.9633</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6918</v>
+        <v>3.242599999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2556</v>
+        <v>-12.1599</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2756</v>
+        <v>-9.111699999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5313</v>
+        <v>-3.0482</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>10.4262</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-16.4119</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5792</v>
+        <v>26.8379</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6013000000000001</v>
+        <v>-0.2829999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4967</v>
+        <v>-0.4259000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1047</v>
+        <v>0.1426999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4554</v>
+        <v>-6.9826</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>10.0645</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4554</v>
+        <v>-17.0471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. RYTZ</t>
+          <t>A. MAÏGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9037</v>
+        <v>-4.3013</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1172</v>
+        <v>-2.1145</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2134</v>
+        <v>-2.1868</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.6357</v>
+        <v>-0.9080999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9998</v>
+        <v>-1.0686</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6358</v>
+        <v>0.1605</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.3101</v>
+        <v>-0.6524</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8266</v>
+        <v>-1.3442</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.4836</v>
+        <v>0.6918</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6744</v>
+        <v>-0.2556</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8268</v>
+        <v>0.2756</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8478</v>
+        <v>-0.5313</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9306</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8964</v>
+        <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1486</v>
+        <v>-0.5516</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0198</v>
+        <v>-0.4967</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8711000000000001</v>
+        <v>-0.05509999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4859</v>
+        <v>-2.4554</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4859</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.336799999999998</v>
+        <v>-6.8528</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7934</v>
+        <v>-9.0029</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5435</v>
+        <v>2.1501</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9542</v>
+        <v>-3.526299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1486</v>
+        <v>-5.7806</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1943999999999995</v>
+        <v>2.254299999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>10.2057</v>
+        <v>6.1546</v>
       </c>
       <c r="K12" t="n">
-        <v>6.9633</v>
+        <v>1.1914</v>
       </c>
       <c r="L12" t="n">
-        <v>3.242599999999999</v>
+        <v>4.963</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.1599</v>
+        <v>-9.6814</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.111699999999999</v>
+        <v>-6.9724</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.0482</v>
+        <v>-2.7089</v>
       </c>
       <c r="P12" t="n">
-        <v>10.4262</v>
+        <v>4.8268</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.4119</v>
+        <v>-17.5704</v>
       </c>
       <c r="R12" t="n">
-        <v>26.8379</v>
+        <v>22.3971</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.8263</v>
+        <v>2.6194</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.651899999999999</v>
+        <v>0.6989000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1746</v>
+        <v>1.9207</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.9826</v>
+        <v>-10.7729</v>
       </c>
       <c r="W12" t="n">
-        <v>10.0645</v>
+        <v>1.7136</v>
       </c>
       <c r="X12" t="n">
-        <v>-17.0471</v>
+        <v>-12.4866</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GABALDÓN CASTELLANOS</t>
+          <t>K. RYTZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6568</v>
+        <v>-7.0732</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2198</v>
+        <v>-10.6344</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.437</v>
+        <v>3.5611</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9933</v>
+        <v>-4.6357</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4968</v>
+        <v>-1.9998</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4965</v>
+        <v>-2.6358</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9443</v>
+        <v>-6.3101</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5653</v>
+        <v>-2.8266</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.379</v>
+        <v>-3.4836</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.049</v>
+        <v>1.6744</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9315</v>
+        <v>0.8268</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1175</v>
+        <v>0.8478</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1238</v>
+        <v>-1.9306</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0893</v>
+        <v>-4.827</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9654</v>
+        <v>2.8964</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2594</v>
+        <v>-0.02080000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.414</v>
+        <v>0.5027</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6733</v>
+        <v>-0.5234000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7989</v>
+        <v>-0.4859</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0266</v>
+        <v>-0.4859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>D. GABALDÓN CASTELLANOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.9806</v>
+        <v>-7.2127</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.3191</v>
+        <v>-3.751</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6613000000000002</v>
+        <v>-3.4618</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.526299999999999</v>
+        <v>-3.9933</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7806</v>
+        <v>-2.4968</v>
       </c>
       <c r="I14" t="n">
-        <v>2.254299999999999</v>
+        <v>-1.4965</v>
       </c>
       <c r="J14" t="n">
-        <v>6.1546</v>
+        <v>-1.9443</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1914</v>
+        <v>-0.5653</v>
       </c>
       <c r="L14" t="n">
-        <v>4.963</v>
+        <v>-1.379</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.6814</v>
+        <v>-2.049</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.9724</v>
+        <v>-1.9315</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7089</v>
+        <v>-0.1175</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8268</v>
+        <v>-2.1238</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.5704</v>
+        <v>-3.0893</v>
       </c>
       <c r="R14" t="n">
-        <v>22.3971</v>
+        <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.5081</v>
+        <v>0.7034</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6174</v>
+        <v>0.0549</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8905</v>
+        <v>0.6485</v>
       </c>
       <c r="V14" t="n">
-        <v>-10.7729</v>
+        <v>-1.7989</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7136</v>
+        <v>1.2277</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.4866</v>
+        <v>-3.0266</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.8345</v>
+        <v>-18.4167</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.2006</v>
+        <v>-13.3797</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.634</v>
+        <v>-5.0368</v>
       </c>
       <c r="G15" t="n">
         <v>-6.9959</v>
@@ -1624,13 +1624,13 @@
         <v>24.1347</v>
       </c>
       <c r="S15" t="n">
-        <v>5.091699999999999</v>
+        <v>3.5099</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5674</v>
+        <v>0.3885000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5246</v>
+        <v>3.1214</v>
       </c>
       <c r="V15" t="n">
         <v>-14.3511</v>
@@ -1657,19 +1657,19 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>279.0388</v>
+        <v>301.3804</v>
       </c>
       <c r="E16" t="n">
-        <v>147.8598</v>
+        <v>152.2736</v>
       </c>
       <c r="F16" t="n">
-        <v>131.1797</v>
+        <v>149.1051</v>
       </c>
       <c r="G16" t="n">
         <v>198.1186</v>
       </c>
       <c r="H16" t="n">
-        <v>128.975</v>
+        <v>128.9750000000001</v>
       </c>
       <c r="I16" t="n">
         <v>69.143</v>
@@ -1699,19 +1699,19 @@
         <v>-356.2316999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>411.2556000000001</v>
+        <v>411.2556</v>
       </c>
       <c r="S16" t="n">
-        <v>52.96230000000001</v>
+        <v>75.3023</v>
       </c>
       <c r="T16" t="n">
-        <v>21.0206</v>
+        <v>25.43520000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>31.94090000000001</v>
+        <v>49.86709999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-27.0687</v>
+        <v>-27.06870000000001</v>
       </c>
       <c r="W16" t="n">
         <v>153.6061</v>
